--- a/regression_results.xlsx
+++ b/regression_results.xlsx
@@ -439,16 +439,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,10 +481,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>F_change</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dR2_p</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>F_p</t>
         </is>
@@ -500,17 +512,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1154</v>
+        <v>0.1148</v>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>2.912</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0106</v>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0153</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +539,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="F3" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="4">
@@ -558,12 +578,18 @@
         <v>0.1377</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="F4" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.2</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -579,17 +605,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1737</v>
+        <v>0.1687</v>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>4.555</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0003</v>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0007</v>
       </c>
     </row>
     <row r="6">
@@ -604,18 +632,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="F6" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="G6" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -637,12 +671,18 @@
         <v>0.2205</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="F7" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="H7" t="n">
         <v>3.834</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -658,17 +698,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1005</v>
+        <v>0.1011</v>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.0499</v>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="9">
@@ -683,19 +725,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="F9" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="10">
@@ -716,12 +764,18 @@
         <v>0.1368</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="F10" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.902</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -737,17 +791,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
-        <v>1.645</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.1364</v>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="12">
@@ -762,19 +818,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="F12" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="13">
@@ -795,12 +857,18 @@
         <v>0.0438</v>
       </c>
       <c r="E13" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.901</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -816,17 +884,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0861</v>
+        <v>0.0849</v>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>3.204</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.005</v>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="15">
@@ -841,19 +911,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="F15" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="16">
@@ -874,12 +950,18 @@
         <v>0.1027</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="F16" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="H16" t="n">
         <v>2.252</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -2682,7 +2764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:R116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2698,9 +2780,11 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2776,10 +2860,20 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>F_change</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dR2_p</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>F_p</t>
         </is>
@@ -2802,28 +2896,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1211</v>
+        <v>0.0675</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0701</v>
+        <v>0.037</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1472</v>
+        <v>0.1574</v>
       </c>
       <c r="H2" t="n">
-        <v>0.823</v>
+        <v>0.429</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4121</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.17</v>
+        <v>-0.244</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4121</v>
+        <v>0.379</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -2831,14 +2925,16 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.1154</v>
+        <v>0.1148</v>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>2.912</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.0106</v>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0153</v>
       </c>
     </row>
     <row r="3">
@@ -2858,28 +2954,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0842</v>
+        <v>-0.0915</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0537</v>
+        <v>-0.0583</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1284</v>
+        <v>0.1318</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.656</v>
+        <v>-0.695</v>
       </c>
       <c r="I3" t="n">
-        <v>0.513</v>
+        <v>0.4886</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3382</v>
+        <v>-0.3522</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1697</v>
+        <v>0.1692</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -2887,14 +2983,16 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.1154</v>
+        <v>0.1148</v>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>2.912</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.0106</v>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0153</v>
       </c>
     </row>
     <row r="4">
@@ -2914,28 +3012,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1896</v>
+        <v>0.1944</v>
       </c>
       <c r="F4" t="n">
-        <v>0.267</v>
+        <v>0.2739</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0604</v>
+        <v>0.0617</v>
       </c>
       <c r="H4" t="n">
-        <v>3.14</v>
+        <v>3.152</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0021</v>
+        <v>0.002</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0702</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.309</v>
+        <v>0.3165</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -2943,14 +3041,16 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.1154</v>
+        <v>0.1148</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>2.912</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.0106</v>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0153</v>
       </c>
     </row>
     <row r="5">
@@ -2970,28 +3070,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0706</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0798</v>
+        <v>0.0728</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0795</v>
+        <v>0.082</v>
       </c>
       <c r="H5" t="n">
-        <v>0.966</v>
+        <v>0.862</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3359</v>
+        <v>0.3906</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0805</v>
+        <v>-0.0916</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2341</v>
+        <v>0.2329</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -2999,14 +3099,16 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.1154</v>
+        <v>0.1148</v>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>2.912</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0106</v>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0153</v>
       </c>
     </row>
     <row r="6">
@@ -3026,28 +3128,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1208</v>
+        <v>-0.137</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0891</v>
+        <v>-0.1013</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1168</v>
+        <v>0.1195</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.034</v>
+        <v>-1.146</v>
       </c>
       <c r="I6" t="n">
-        <v>0.303</v>
+        <v>0.254</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3519</v>
+        <v>-0.3735</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1103</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -3055,14 +3157,16 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1154</v>
+        <v>0.1148</v>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>2.912</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0106</v>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0153</v>
       </c>
     </row>
     <row r="7">
@@ -3082,28 +3186,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0761</v>
+        <v>0.0853</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1232</v>
+        <v>0.1362</v>
       </c>
       <c r="G7" t="n">
-        <v>0.053</v>
+        <v>0.0552</v>
       </c>
       <c r="H7" t="n">
-        <v>1.436</v>
+        <v>1.546</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1535</v>
+        <v>0.1246</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0288</v>
+        <v>-0.0239</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1811</v>
+        <v>0.1945</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -3111,14 +3215,16 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.1154</v>
+        <v>0.1148</v>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>2.912</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.0106</v>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0153</v>
       </c>
     </row>
     <row r="8">
@@ -3138,28 +3244,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.14</v>
+        <v>-0.1455</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0798</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2022</v>
+        <v>0.2027</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4901</v>
+        <v>0.4743</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5401</v>
+        <v>-0.5467</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2602</v>
+        <v>0.2557</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -3167,16 +3273,22 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="O8" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="9">
@@ -3196,28 +3308,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0975</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0621</v>
+        <v>-0.0581</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1319</v>
+        <v>0.1324</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.739</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4612</v>
+        <v>0.4918</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3585</v>
+        <v>-0.3533</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1635</v>
+        <v>0.1708</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -3225,16 +3337,22 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="O9" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="10">
@@ -3254,28 +3372,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1932</v>
+        <v>0.1971</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2731</v>
+        <v>0.2777</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0611</v>
+        <v>0.0615</v>
       </c>
       <c r="H10" t="n">
-        <v>3.159</v>
+        <v>3.206</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002</v>
+        <v>0.0017</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0722</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3141</v>
+        <v>0.3188</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -3283,16 +3401,22 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="O10" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="11">
@@ -3312,28 +3436,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0759</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0818</v>
       </c>
       <c r="H11" t="n">
-        <v>0.924</v>
+        <v>0.928</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3574</v>
+        <v>0.355</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0861</v>
+        <v>-0.0859</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2369</v>
+        <v>0.2377</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -3341,16 +3465,22 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="O11" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="12">
@@ -3370,28 +3500,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1825</v>
+        <v>-0.1788</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.135</v>
+        <v>-0.1323</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1215</v>
+        <v>0.1218</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.502</v>
+        <v>-1.468</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1355</v>
+        <v>0.1447</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4229</v>
+        <v>-0.4199</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0579</v>
+        <v>0.0623</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -3399,16 +3529,22 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="O12" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="13">
@@ -3428,28 +3564,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0697</v>
+        <v>0.0733</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1114</v>
+        <v>0.1171</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0551</v>
+        <v>0.0554</v>
       </c>
       <c r="H13" t="n">
-        <v>1.264</v>
+        <v>1.323</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2085</v>
+        <v>0.1883</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0394</v>
+        <v>-0.0364</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1787</v>
+        <v>0.1831</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -3457,16 +3593,22 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="O13" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="14">
@@ -3486,28 +3628,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6836</v>
+        <v>0.6734</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1613</v>
+        <v>0.1589</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5427</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.26</v>
+        <v>1.238</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2101</v>
+        <v>0.218</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3902</v>
+        <v>-0.403</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7575</v>
+        <v>1.7498</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -3515,16 +3657,22 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="O14" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="15">
@@ -3544,28 +3692,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3143</v>
+        <v>0.3062</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0438</v>
+        <v>0.0427</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7651</v>
       </c>
       <c r="H15" t="n">
-        <v>0.412</v>
+        <v>0.4</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6813</v>
+        <v>0.6897</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1968</v>
+        <v>-1.2081</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8254</v>
+        <v>1.8204</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3721,22 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.1327</v>
+        <v>0.1348</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0173</v>
+        <v>0.02</v>
       </c>
       <c r="O15" t="n">
-        <v>2.409</v>
+        <v>1.445</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0187</v>
+        <v>0.2397</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="16">
@@ -3634,12 +3788,18 @@
         <v>0.1377</v>
       </c>
       <c r="N16" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O16" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.2</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -3692,12 +3852,18 @@
         <v>0.1377</v>
       </c>
       <c r="N17" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O17" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2.2</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -3750,12 +3916,18 @@
         <v>0.1377</v>
       </c>
       <c r="N18" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O18" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.2</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -3808,12 +3980,18 @@
         <v>0.1377</v>
       </c>
       <c r="N19" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O19" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.2</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -3866,12 +4044,18 @@
         <v>0.1377</v>
       </c>
       <c r="N20" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O20" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.2</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -3924,12 +4108,18 @@
         <v>0.1377</v>
       </c>
       <c r="N21" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O21" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.2</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -3982,12 +4172,18 @@
         <v>0.1377</v>
       </c>
       <c r="N22" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O22" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -4040,12 +4236,18 @@
         <v>0.1377</v>
       </c>
       <c r="N23" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O23" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -4098,12 +4300,18 @@
         <v>0.1377</v>
       </c>
       <c r="N24" t="n">
-        <v>0.005</v>
+        <v>0.0028</v>
       </c>
       <c r="O24" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.2</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.0263</v>
       </c>
     </row>
@@ -4124,28 +4332,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3126</v>
+        <v>0.306</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1996</v>
+        <v>0.1879</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1294</v>
+        <v>0.1366</v>
       </c>
       <c r="H25" t="n">
-        <v>2.416</v>
+        <v>2.24</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0171</v>
+        <v>0.0268</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0567</v>
+        <v>0.0357</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5685</v>
+        <v>0.5762</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -4153,14 +4361,16 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.1737</v>
+        <v>0.1687</v>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>4.555</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.0003</v>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.0007</v>
       </c>
     </row>
     <row r="26">
@@ -4180,28 +4390,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1288</v>
+        <v>-0.1251</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0907</v>
+        <v>-0.0876</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1141</v>
+        <v>0.1172</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.129</v>
+        <v>-1.067</v>
       </c>
       <c r="I26" t="n">
-        <v>0.261</v>
+        <v>0.2879</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3545</v>
+        <v>-0.357</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0969</v>
+        <v>0.1069</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -4209,14 +4419,16 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.1737</v>
+        <v>0.1687</v>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>4.555</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.0003</v>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.0007</v>
       </c>
     </row>
     <row r="27">
@@ -4236,28 +4448,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1649</v>
+        <v>0.165</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2589</v>
+        <v>0.2583</v>
       </c>
       <c r="G27" t="n">
-        <v>0.053</v>
+        <v>0.0543</v>
       </c>
       <c r="H27" t="n">
-        <v>3.11</v>
+        <v>3.041</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0023</v>
+        <v>0.0029</v>
       </c>
       <c r="J27" t="n">
-        <v>0.06</v>
+        <v>0.0576</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2698</v>
+        <v>0.2723</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -4265,14 +4477,16 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.1737</v>
+        <v>0.1687</v>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>4.555</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.0003</v>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.0007</v>
       </c>
     </row>
     <row r="28">
@@ -4292,28 +4506,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0467</v>
+        <v>0.0438</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0538</v>
+        <v>0.05</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0702</v>
+        <v>0.0722</v>
       </c>
       <c r="H28" t="n">
-        <v>0.665</v>
+        <v>0.606</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5072</v>
+        <v>0.5456</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1857</v>
+        <v>0.1866</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -4321,14 +4535,16 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.1737</v>
+        <v>0.1687</v>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>4.555</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.0003</v>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.0007</v>
       </c>
     </row>
     <row r="29">
@@ -4348,28 +4564,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1266</v>
+        <v>-0.127</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1047</v>
+        <v>-0.1048</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1025</v>
+        <v>0.105</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.235</v>
+        <v>-1.209</v>
       </c>
       <c r="I29" t="n">
-        <v>0.219</v>
+        <v>0.2288</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3294</v>
+        <v>-0.3349</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0762</v>
+        <v>0.0809</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -4377,14 +4593,16 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.1737</v>
+        <v>0.1687</v>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>4.555</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.0003</v>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.0007</v>
       </c>
     </row>
     <row r="30">
@@ -4404,28 +4622,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0868</v>
+        <v>0.0907</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1509</v>
+        <v>0.1576</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0484</v>
+        <v>0.0495</v>
       </c>
       <c r="H30" t="n">
-        <v>1.792</v>
+        <v>1.832</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0755</v>
+        <v>0.0694</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.0073</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1825</v>
+        <v>0.1887</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -4433,14 +4651,16 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.1737</v>
+        <v>0.1687</v>
       </c>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>4.555</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.0003</v>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.0007</v>
       </c>
     </row>
     <row r="31">
@@ -4460,28 +4680,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0607</v>
+        <v>0.0581</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0373</v>
+        <v>0.0357</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1737</v>
+        <v>0.1744</v>
       </c>
       <c r="H31" t="n">
-        <v>0.349</v>
+        <v>0.333</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7275</v>
+        <v>0.7398</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2832</v>
+        <v>-0.2872</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4045</v>
+        <v>0.4033</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -4489,15 +4709,21 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="O31" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="P31" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -4518,28 +4744,28 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1051</v>
+        <v>-0.1019</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0738</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1151</v>
+        <v>0.1157</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.913</v>
+        <v>-0.881</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3629</v>
+        <v>0.3799</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3328</v>
+        <v>-0.3309</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1227</v>
+        <v>0.127</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -4547,15 +4773,21 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="O32" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="P32" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -4576,28 +4808,28 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1676</v>
+        <v>0.1695</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2634</v>
+        <v>0.2654</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0527</v>
+        <v>0.0531</v>
       </c>
       <c r="H33" t="n">
-        <v>3.18</v>
+        <v>3.195</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0633</v>
+        <v>0.0645</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2719</v>
+        <v>0.2746</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
@@ -4605,15 +4837,21 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="O33" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="P33" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -4634,28 +4872,28 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0514</v>
+        <v>0.0516</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0587</v>
+        <v>0.059</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0704</v>
+        <v>0.0706</v>
       </c>
       <c r="H34" t="n">
-        <v>0.729</v>
+        <v>0.731</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4672</v>
+        <v>0.4664</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.0882</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1907</v>
+        <v>0.1914</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -4663,15 +4901,21 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="O34" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="P34" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -4692,28 +4936,28 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1872</v>
+        <v>-0.1854</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1545</v>
+        <v>-0.1529</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1045</v>
+        <v>0.1049</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.792</v>
+        <v>-1.767</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0756</v>
+        <v>0.0796</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3939</v>
+        <v>-0.393</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0196</v>
+        <v>0.0222</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
@@ -4721,15 +4965,21 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="O35" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="P35" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -4750,28 +5000,28 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0735</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1281</v>
+        <v>0.1311</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0484</v>
+        <v>0.0488</v>
       </c>
       <c r="H36" t="n">
-        <v>1.518</v>
+        <v>1.546</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1315</v>
+        <v>0.1246</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.0223</v>
+        <v>-0.0211</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1694</v>
+        <v>0.172</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -4779,15 +5029,21 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="O36" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="P36" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R36" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -4808,28 +5064,28 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4765</v>
+        <v>0.4712</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1252</v>
+        <v>0.1237</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4706</v>
+        <v>0.4723</v>
       </c>
       <c r="H37" t="n">
-        <v>1.013</v>
+        <v>0.998</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3132</v>
+        <v>0.3204</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4549</v>
+        <v>-0.4637</v>
       </c>
       <c r="K37" t="n">
-        <v>1.4079</v>
+        <v>1.406</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -4837,15 +5093,21 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="O37" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="P37" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R37" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -4866,28 +5128,28 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E38" t="n">
-        <v>1.1643</v>
+        <v>1.1609</v>
       </c>
       <c r="F38" t="n">
-        <v>0.182</v>
+        <v>0.1814</v>
       </c>
       <c r="G38" t="n">
-        <v>0.657</v>
+        <v>0.6592</v>
       </c>
       <c r="H38" t="n">
-        <v>1.772</v>
+        <v>1.761</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0788</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1361</v>
+        <v>-0.1439</v>
       </c>
       <c r="K38" t="n">
-        <v>2.4646</v>
+        <v>2.4658</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -4895,15 +5157,21 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.2174</v>
+        <v>0.2181</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0437</v>
+        <v>0.0494</v>
       </c>
       <c r="O38" t="n">
-        <v>4.307</v>
+        <v>3.886</v>
       </c>
       <c r="P38" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R38" t="n">
         <v>0.0001</v>
       </c>
     </row>
@@ -4956,12 +5224,18 @@
         <v>0.2205</v>
       </c>
       <c r="N39" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O39" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3.834</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5014,12 +5288,18 @@
         <v>0.2205</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O40" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3.834</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5072,12 +5352,18 @@
         <v>0.2205</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O41" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q41" t="n">
         <v>3.834</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5130,12 +5416,18 @@
         <v>0.2205</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O42" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q42" t="n">
         <v>3.834</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5188,12 +5480,18 @@
         <v>0.2205</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O43" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q43" t="n">
         <v>3.834</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5246,12 +5544,18 @@
         <v>0.2205</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O44" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q44" t="n">
         <v>3.834</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5304,12 +5608,18 @@
         <v>0.2205</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O45" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q45" t="n">
         <v>3.834</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5362,12 +5672,18 @@
         <v>0.2205</v>
       </c>
       <c r="N46" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O46" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q46" t="n">
         <v>3.834</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5420,12 +5736,18 @@
         <v>0.2205</v>
       </c>
       <c r="N47" t="n">
-        <v>0.0031</v>
+        <v>0.0024</v>
       </c>
       <c r="O47" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q47" t="n">
         <v>3.834</v>
       </c>
-      <c r="P47" t="n">
+      <c r="R47" t="n">
         <v>0.0003</v>
       </c>
     </row>
@@ -5446,28 +5768,28 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0051</v>
+        <v>-0.0569</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0029</v>
+        <v>-0.0308</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1615</v>
+        <v>0.171</v>
       </c>
       <c r="H48" t="n">
-        <v>0.032</v>
+        <v>-0.333</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9748</v>
+        <v>0.7398</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.3147</v>
+        <v>-0.3957</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3249</v>
+        <v>0.2819</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -5475,14 +5797,16 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.1005</v>
+        <v>0.1011</v>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.0499</v>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="49">
@@ -5502,43 +5826,45 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.2901</v>
+        <v>-0.3065</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1736</v>
+        <v>-0.1822</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1484</v>
+        <v>0.153</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.955</v>
+        <v>-2.003</v>
       </c>
       <c r="I49" t="n">
-        <v>0.053</v>
+        <v>0.0476</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.5841</v>
+        <v>-0.6098</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0038</v>
+        <v>-0.0033</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>*</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.1005</v>
+        <v>0.1011</v>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0.0499</v>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="50">
@@ -5558,28 +5884,28 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1583</v>
+        <v>0.1628</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2093</v>
+        <v>0.214</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0696</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>2.273</v>
+        <v>2.279</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0249</v>
+        <v>0.0246</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0204</v>
+        <v>0.0212</v>
       </c>
       <c r="K50" t="n">
-        <v>0.2961</v>
+        <v>0.3044</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
@@ -5587,14 +5913,16 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.1005</v>
+        <v>0.1011</v>
       </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0.0499</v>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="51">
@@ -5614,28 +5942,28 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0757</v>
+        <v>0.0634</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0762</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0888</v>
+        <v>0.0919</v>
       </c>
       <c r="H51" t="n">
-        <v>0.852</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3957</v>
+        <v>0.4917</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.1001</v>
+        <v>-0.1188</v>
       </c>
       <c r="K51" t="n">
-        <v>0.2515</v>
+        <v>0.2456</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -5643,14 +5971,16 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.1005</v>
+        <v>0.1011</v>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0.0499</v>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="52">
@@ -5670,28 +6000,28 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0712</v>
+        <v>-0.0701</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0508</v>
+        <v>-0.0499</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1301</v>
+        <v>0.1338</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.547</v>
+        <v>-0.524</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5851</v>
+        <v>0.6012</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.3289</v>
+        <v>-0.3352</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1865</v>
+        <v>0.1949</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -5699,14 +6029,16 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.1005</v>
+        <v>0.1011</v>
       </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0.0499</v>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="53">
@@ -5726,43 +6058,45 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1064</v>
+        <v>0.1068</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1573</v>
+        <v>0.1562</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0629</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>1.691</v>
+        <v>1.639</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0935</v>
+        <v>0.1041</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.0182</v>
+        <v>-0.0223</v>
       </c>
       <c r="K53" t="n">
-        <v>0.2311</v>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>t</t>
+        <v>0.2359</v>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.1005</v>
+        <v>0.1011</v>
       </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0.0499</v>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="54">
@@ -5782,28 +6116,28 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3289</v>
+        <v>-0.3355</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1782</v>
+        <v>-0.1818</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2178</v>
+        <v>0.2183</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.51</v>
+        <v>-1.537</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1338</v>
+        <v>0.1272</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.7605</v>
+        <v>-0.7682</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1027</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -5811,16 +6145,22 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="O54" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="55">
@@ -5840,28 +6180,28 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3208</v>
+        <v>-0.3136</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1909</v>
+        <v>-0.1864</v>
       </c>
       <c r="G55" t="n">
-        <v>0.153</v>
+        <v>0.1535</v>
       </c>
       <c r="H55" t="n">
-        <v>-2.097</v>
+        <v>-2.042</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0383</v>
+        <v>0.0435</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.624</v>
+        <v>-0.6179</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.0176</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
@@ -5869,16 +6209,22 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="N55" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="O55" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="P55" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="56">
@@ -5898,28 +6244,28 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1621</v>
+        <v>0.1669</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2138</v>
+        <v>0.2194</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0704</v>
+        <v>0.0708</v>
       </c>
       <c r="H56" t="n">
-        <v>2.302</v>
+        <v>2.357</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0232</v>
+        <v>0.0202</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0225</v>
+        <v>0.0266</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3016</v>
+        <v>0.3072</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -5927,16 +6273,22 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="N56" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="O56" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="P56" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="57">
@@ -5956,28 +6308,28 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0679</v>
+        <v>0.0689</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0675</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>0.091</v>
+        <v>0.0912</v>
       </c>
       <c r="H57" t="n">
-        <v>0.746</v>
+        <v>0.756</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4575</v>
+        <v>0.4514</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.1125</v>
+        <v>-0.1118</v>
       </c>
       <c r="K57" t="n">
-        <v>0.2482</v>
+        <v>0.2496</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
@@ -5985,16 +6337,22 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="N57" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="O57" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="P57" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="58">
@@ -6014,28 +6372,28 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1245</v>
+        <v>-0.1201</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.0886</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1349</v>
+        <v>0.1353</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.923</v>
+        <v>-0.887</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3581</v>
+        <v>0.3768</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.3919</v>
+        <v>-0.3882</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1429</v>
+        <v>0.1481</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -6043,16 +6401,22 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="N58" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="O58" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="P58" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="59">
@@ -6072,28 +6436,28 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0857</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1255</v>
+        <v>0.1323</v>
       </c>
       <c r="G59" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>1.325</v>
+        <v>1.39</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1879</v>
+        <v>0.1675</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.0425</v>
+        <v>-0.0385</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2138</v>
+        <v>0.2194</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -6101,16 +6465,22 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="N59" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="O59" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="P59" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="60">
@@ -6130,28 +6500,28 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E60" t="n">
-        <v>1.0537</v>
+        <v>1.0402</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2443</v>
+        <v>0.2412</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5889</v>
+        <v>0.5903</v>
       </c>
       <c r="H60" t="n">
-        <v>1.789</v>
+        <v>1.762</v>
       </c>
       <c r="I60" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0808</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.1134</v>
+        <v>-0.1296</v>
       </c>
       <c r="K60" t="n">
-        <v>2.2209</v>
+        <v>2.2101</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
@@ -6159,16 +6529,22 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="N60" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="O60" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="P60" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="61">
@@ -6188,28 +6564,28 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0166</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0012</v>
+        <v>-0.0023</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8266</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9915</v>
+        <v>0.9841</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.647</v>
+        <v>-1.6579</v>
       </c>
       <c r="K61" t="n">
-        <v>1.6293</v>
+        <v>1.6248</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
@@ -6217,16 +6593,22 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.1318</v>
+        <v>0.1337</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0314</v>
+        <v>0.0325</v>
       </c>
       <c r="O61" t="n">
-        <v>2.088</v>
+        <v>2.047</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0429</v>
+        <v>0.134</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="62">
@@ -6278,12 +6660,18 @@
         <v>0.1368</v>
       </c>
       <c r="N62" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O62" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q62" t="n">
         <v>1.902</v>
       </c>
-      <c r="P62" t="n">
+      <c r="R62" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6336,12 +6724,18 @@
         <v>0.1368</v>
       </c>
       <c r="N63" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O63" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q63" t="n">
         <v>1.902</v>
       </c>
-      <c r="P63" t="n">
+      <c r="R63" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6394,12 +6788,18 @@
         <v>0.1368</v>
       </c>
       <c r="N64" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O64" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q64" t="n">
         <v>1.902</v>
       </c>
-      <c r="P64" t="n">
+      <c r="R64" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6452,12 +6852,18 @@
         <v>0.1368</v>
       </c>
       <c r="N65" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O65" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q65" t="n">
         <v>1.902</v>
       </c>
-      <c r="P65" t="n">
+      <c r="R65" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6510,12 +6916,18 @@
         <v>0.1368</v>
       </c>
       <c r="N66" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O66" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q66" t="n">
         <v>1.902</v>
       </c>
-      <c r="P66" t="n">
+      <c r="R66" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6568,12 +6980,18 @@
         <v>0.1368</v>
       </c>
       <c r="N67" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O67" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q67" t="n">
         <v>1.902</v>
       </c>
-      <c r="P67" t="n">
+      <c r="R67" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6626,12 +7044,18 @@
         <v>0.1368</v>
       </c>
       <c r="N68" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O68" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q68" t="n">
         <v>1.902</v>
       </c>
-      <c r="P68" t="n">
+      <c r="R68" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6684,12 +7108,18 @@
         <v>0.1368</v>
       </c>
       <c r="N69" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O69" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q69" t="n">
         <v>1.902</v>
       </c>
-      <c r="P69" t="n">
+      <c r="R69" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6742,12 +7172,18 @@
         <v>0.1368</v>
       </c>
       <c r="N70" t="n">
-        <v>0.005</v>
+        <v>0.0032</v>
       </c>
       <c r="O70" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="Q70" t="n">
         <v>1.902</v>
       </c>
-      <c r="P70" t="n">
+      <c r="R70" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6768,28 +7204,28 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1535</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1045</v>
+        <v>0.0407</v>
       </c>
       <c r="G71" t="n">
-        <v>0.1054</v>
+        <v>0.1264</v>
       </c>
       <c r="H71" t="n">
-        <v>1.456</v>
+        <v>0.527</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1469</v>
+        <v>0.5988</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.0543</v>
+        <v>-0.1828</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3613</v>
+        <v>0.316</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
@@ -6797,14 +7233,16 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="n">
-        <v>1.645</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0.1364</v>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="72">
@@ -6824,28 +7262,28 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.0072</v>
+        <v>-0.0423</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.0056</v>
+        <v>-0.034</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0893</v>
+        <v>0.0917</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.08</v>
+        <v>-0.461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9361</v>
+        <v>0.6453</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.1833</v>
+        <v>-0.2232</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1689</v>
+        <v>0.1386</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
@@ -6853,14 +7291,16 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="n">
-        <v>1.645</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0.1364</v>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="73">
@@ -6880,28 +7320,28 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0177</v>
+        <v>0.0157</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0285</v>
+        <v>0.0263</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0436</v>
+        <v>0.0449</v>
       </c>
       <c r="H73" t="n">
-        <v>0.405</v>
+        <v>0.35</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6857</v>
+        <v>0.7266</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.0682</v>
+        <v>-0.0728</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1035</v>
+        <v>0.1042</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
@@ -6909,14 +7349,16 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="n">
-        <v>1.645</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0.1364</v>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="74">
@@ -6936,28 +7378,28 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1071</v>
+        <v>0.106</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1257</v>
+        <v>0.1325</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0589</v>
+        <v>0.0593</v>
       </c>
       <c r="H74" t="n">
-        <v>1.817</v>
+        <v>1.788</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0707</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.0091</v>
+        <v>-0.011</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2232</v>
+        <v>0.2231</v>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
@@ -6965,14 +7407,16 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="n">
-        <v>1.645</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0.1364</v>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="75">
@@ -6992,28 +7436,28 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.0112</v>
+        <v>-0.0447</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.0168</v>
+        <v>-0.0688</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0482</v>
+        <v>0.0505</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.232</v>
+        <v>-0.886</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8166</v>
+        <v>0.3769</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.1063</v>
+        <v>-0.1444</v>
       </c>
       <c r="K75" t="n">
-        <v>0.0839</v>
+        <v>0.0549</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
@@ -7021,14 +7465,16 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="n">
-        <v>1.645</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0.1364</v>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="76">
@@ -7048,28 +7494,28 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0548</v>
+        <v>0.0505</v>
       </c>
       <c r="F76" t="n">
-        <v>0.112</v>
+        <v>0.1061</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0361</v>
+        <v>0.0373</v>
       </c>
       <c r="H76" t="n">
-        <v>1.518</v>
+        <v>1.355</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1304</v>
+        <v>0.1771</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.0164</v>
+        <v>-0.023</v>
       </c>
       <c r="K76" t="n">
-        <v>0.126</v>
+        <v>0.1241</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
@@ -7077,14 +7523,16 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>0.0461</v>
+        <v>0.0399</v>
       </c>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>1.645</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0.1364</v>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="77">
@@ -7104,28 +7552,28 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0544</v>
+        <v>0.0289</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0323</v>
+        <v>0.0176</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1716</v>
+        <v>0.1676</v>
       </c>
       <c r="H77" t="n">
-        <v>0.317</v>
+        <v>0.172</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7516</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.2842</v>
+        <v>-0.3019</v>
       </c>
       <c r="K77" t="n">
-        <v>0.393</v>
+        <v>0.3596</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -7133,16 +7581,22 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="N77" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="O77" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="P77" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="78">
@@ -7162,28 +7616,28 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.0499</v>
+        <v>-0.0356</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.0393</v>
+        <v>-0.0286</v>
       </c>
       <c r="G78" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0926</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.53</v>
+        <v>-0.384</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5971</v>
+        <v>0.7012</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.2358</v>
+        <v>-0.2183</v>
       </c>
       <c r="K78" t="n">
-        <v>0.136</v>
+        <v>0.1471</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -7191,16 +7645,22 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="N78" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="O78" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="P78" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="79">
@@ -7220,28 +7680,28 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0015</v>
+        <v>0.0147</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0025</v>
+        <v>0.0246</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0459</v>
+        <v>0.045</v>
       </c>
       <c r="H79" t="n">
-        <v>0.033</v>
+        <v>0.325</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9734</v>
+        <v>0.7452</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.0891</v>
+        <v>-0.0742</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0921</v>
+        <v>0.1035</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -7249,16 +7709,22 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="N79" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="O79" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="P79" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="80">
@@ -7278,45 +7744,51 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0984</v>
+        <v>0.1078</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1199</v>
+        <v>0.1347</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0609</v>
+        <v>0.0596</v>
       </c>
       <c r="H80" t="n">
-        <v>1.616</v>
+        <v>1.809</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1077</v>
+        <v>0.0722</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.0217</v>
+        <v>-0.0098</v>
       </c>
       <c r="K80" t="n">
-        <v>0.2185</v>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>ns</t>
+        <v>0.2254</v>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>t</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="O80" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="P80" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="81">
@@ -7336,28 +7808,28 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.0261</v>
+        <v>-0.044</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.0395</v>
+        <v>-0.0677</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0512</v>
+        <v>0.0507</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.51</v>
+        <v>-0.868</v>
       </c>
       <c r="I81" t="n">
-        <v>0.6108</v>
+        <v>0.3867</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.127</v>
+        <v>-0.1441</v>
       </c>
       <c r="K81" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0561</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
@@ -7365,16 +7837,22 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="N81" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="O81" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="P81" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="82">
@@ -7394,28 +7872,28 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0432</v>
+        <v>0.0486</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0893</v>
+        <v>0.1021</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0381</v>
+        <v>0.0376</v>
       </c>
       <c r="H82" t="n">
-        <v>1.135</v>
+        <v>1.295</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2579</v>
+        <v>0.197</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.0319</v>
+        <v>-0.0255</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1184</v>
+        <v>0.1227</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -7423,16 +7901,22 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="N82" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="O82" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="P82" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="83">
@@ -7452,28 +7936,28 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.0437</v>
+        <v>-0.0611</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.0111</v>
+        <v>-0.0159</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4614</v>
+        <v>0.4504</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.095</v>
+        <v>-0.136</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9246</v>
+        <v>0.8923</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.9498</v>
       </c>
       <c r="K83" t="n">
-        <v>0.8667</v>
+        <v>0.8277</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -7481,16 +7965,22 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="N83" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="O83" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="P83" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="84">
@@ -7510,28 +8000,28 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E84" t="n">
-        <v>0.5183</v>
+        <v>0.5002</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0775</v>
+        <v>0.0769</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6441</v>
+        <v>0.6287</v>
       </c>
       <c r="H84" t="n">
-        <v>0.805</v>
+        <v>0.796</v>
       </c>
       <c r="I84" t="n">
-        <v>0.422</v>
+        <v>0.4274</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.7405</v>
       </c>
       <c r="K84" t="n">
-        <v>1.7892</v>
+        <v>1.7408</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -7539,16 +8029,22 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>0.0359</v>
+        <v>0.0438</v>
       </c>
       <c r="N84" t="n">
-        <v>-0.0102</v>
+        <v>0.004</v>
       </c>
       <c r="O84" t="n">
-        <v>0.843</v>
+        <v>0.368</v>
       </c>
       <c r="P84" t="n">
-        <v>0.5656</v>
+        <v>0.6928</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.4229</v>
       </c>
     </row>
     <row r="85">
@@ -7600,12 +8096,18 @@
         <v>0.0438</v>
       </c>
       <c r="N85" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q85" t="n">
         <v>0.901</v>
       </c>
-      <c r="P85" t="n">
+      <c r="R85" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -7658,12 +8160,18 @@
         <v>0.0438</v>
       </c>
       <c r="N86" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q86" t="n">
         <v>0.901</v>
       </c>
-      <c r="P86" t="n">
+      <c r="R86" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -7716,12 +8224,18 @@
         <v>0.0438</v>
       </c>
       <c r="N87" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q87" t="n">
         <v>0.901</v>
       </c>
-      <c r="P87" t="n">
+      <c r="R87" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -7774,12 +8288,18 @@
         <v>0.0438</v>
       </c>
       <c r="N88" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q88" t="n">
         <v>0.901</v>
       </c>
-      <c r="P88" t="n">
+      <c r="R88" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -7832,12 +8352,18 @@
         <v>0.0438</v>
       </c>
       <c r="N89" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q89" t="n">
         <v>0.901</v>
       </c>
-      <c r="P89" t="n">
+      <c r="R89" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -7890,12 +8416,18 @@
         <v>0.0438</v>
       </c>
       <c r="N90" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q90" t="n">
         <v>0.901</v>
       </c>
-      <c r="P90" t="n">
+      <c r="R90" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -7948,12 +8480,18 @@
         <v>0.0438</v>
       </c>
       <c r="N91" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q91" t="n">
         <v>0.901</v>
       </c>
-      <c r="P91" t="n">
+      <c r="R91" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -8006,12 +8544,18 @@
         <v>0.0438</v>
       </c>
       <c r="N92" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q92" t="n">
         <v>0.901</v>
       </c>
-      <c r="P92" t="n">
+      <c r="R92" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -8064,12 +8608,18 @@
         <v>0.0438</v>
       </c>
       <c r="N93" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="Q93" t="n">
         <v>0.901</v>
       </c>
-      <c r="P93" t="n">
+      <c r="R93" t="n">
         <v>0.5255</v>
       </c>
     </row>
@@ -8090,28 +8640,28 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1334</v>
+        <v>0.0902</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0921</v>
+        <v>0.0546</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1018</v>
+        <v>0.1243</v>
       </c>
       <c r="H94" t="n">
-        <v>1.31</v>
+        <v>0.725</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1916</v>
+        <v>0.4693</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.0673</v>
+        <v>-0.1552</v>
       </c>
       <c r="K94" t="n">
-        <v>0.334</v>
+        <v>0.3355</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
@@ -8119,14 +8669,16 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>0.0861</v>
+        <v>0.0849</v>
       </c>
       <c r="N94" t="inlineStr"/>
-      <c r="O94" t="n">
-        <v>3.204</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0.005</v>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="95">
@@ -8146,28 +8698,28 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.0454</v>
+        <v>-0.0857</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.0357</v>
+        <v>-0.0683</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0863</v>
+        <v>0.0902</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.526</v>
+        <v>-0.95</v>
       </c>
       <c r="I95" t="n">
-        <v>0.5992</v>
+        <v>0.3435</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.2155</v>
+        <v>-0.2636</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1247</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
@@ -8175,14 +8727,16 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>0.0861</v>
+        <v>0.0849</v>
       </c>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="n">
-        <v>3.204</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0.005</v>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="96">
@@ -8202,28 +8756,28 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0936</v>
+        <v>0.0896</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1532</v>
+        <v>0.149</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0421</v>
+        <v>0.0441</v>
       </c>
       <c r="H96" t="n">
-        <v>2.226</v>
+        <v>2.031</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0271</v>
+        <v>0.0438</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0107</v>
+        <v>0.0025</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1766</v>
+        <v>0.1767</v>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
@@ -8231,14 +8785,16 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>0.0861</v>
+        <v>0.0849</v>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>3.204</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0.005</v>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="97">
@@ -8258,28 +8814,28 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0992</v>
+        <v>0.0999</v>
       </c>
       <c r="F97" t="n">
-        <v>0.118</v>
+        <v>0.1239</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0569</v>
+        <v>0.0583</v>
       </c>
       <c r="H97" t="n">
-        <v>1.744</v>
+        <v>1.712</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0827</v>
+        <v>0.0885</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.013</v>
+        <v>-0.0152</v>
       </c>
       <c r="K97" t="n">
-        <v>0.2114</v>
+        <v>0.215</v>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
@@ -8287,14 +8843,16 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>0.0861</v>
+        <v>0.0849</v>
       </c>
       <c r="N97" t="inlineStr"/>
-      <c r="O97" t="n">
-        <v>3.204</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0.005</v>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="98">
@@ -8314,28 +8872,28 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.0293</v>
+        <v>-0.057</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.0446</v>
+        <v>-0.0871</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0466</v>
+        <v>0.0497</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.629</v>
+        <v>-1.148</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5301</v>
+        <v>0.2525</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.1211</v>
+        <v>-0.1551</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0625</v>
+        <v>0.041</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
@@ -8343,14 +8901,16 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>0.0861</v>
+        <v>0.0849</v>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="n">
-        <v>3.204</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0.005</v>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="99">
@@ -8370,28 +8930,28 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0746</v>
+        <v>0.0726</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1546</v>
+        <v>0.1512</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0349</v>
+        <v>0.0367</v>
       </c>
       <c r="H99" t="n">
-        <v>2.14</v>
+        <v>1.979</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0335</v>
+        <v>0.0494</v>
       </c>
       <c r="J99" t="n">
-        <v>0.0059</v>
+        <v>0.0002</v>
       </c>
       <c r="K99" t="n">
-        <v>0.1434</v>
+        <v>0.1449</v>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
@@ -8399,14 +8959,16 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>0.0861</v>
+        <v>0.0849</v>
       </c>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="n">
-        <v>3.204</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0.005</v>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="100">
@@ -8426,28 +8988,28 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.0815</v>
+        <v>-0.0984</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.0489</v>
+        <v>-0.0596</v>
       </c>
       <c r="G100" t="n">
-        <v>0.1648</v>
+        <v>0.1636</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.494</v>
+        <v>-0.601</v>
       </c>
       <c r="I100" t="n">
-        <v>0.6216</v>
+        <v>0.5484</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.4067</v>
+        <v>-0.4213</v>
       </c>
       <c r="K100" t="n">
-        <v>0.2437</v>
+        <v>0.2245</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
@@ -8455,16 +9017,22 @@
         </is>
       </c>
       <c r="M100" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="N100" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="O100" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="P100" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="101">
@@ -8484,28 +9052,28 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.092</v>
+        <v>-0.0848</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.0732</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0905</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>-1.017</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3106</v>
+        <v>0.3496</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.2706</v>
+        <v>-0.2631</v>
       </c>
       <c r="K101" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -8513,16 +9081,22 @@
         </is>
       </c>
       <c r="M101" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="N101" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="O101" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="P101" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="102">
@@ -8542,45 +9116,51 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0808</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1337</v>
+        <v>0.1455</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0441</v>
+        <v>0.044</v>
       </c>
       <c r="H102" t="n">
-        <v>1.832</v>
+        <v>1.99</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0687</v>
+        <v>0.0481</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.0062</v>
+        <v>0.0008</v>
       </c>
       <c r="K102" t="n">
-        <v>0.1678</v>
+        <v>0.1743</v>
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>*</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="N102" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="O102" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="P102" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="103">
@@ -8600,45 +9180,51 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0963</v>
+        <v>0.1053</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1185</v>
+        <v>0.1306</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0585</v>
+        <v>0.0582</v>
       </c>
       <c r="H103" t="n">
-        <v>1.647</v>
+        <v>1.81</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1013</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.0191</v>
+        <v>-0.0095</v>
       </c>
       <c r="K103" t="n">
-        <v>0.2117</v>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>ns</t>
+        <v>0.2201</v>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>t</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="N103" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="O103" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="P103" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="104">
@@ -8658,28 +9244,28 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.0397</v>
+        <v>-0.0575</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.0608</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0491</v>
+        <v>0.0495</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-1.162</v>
       </c>
       <c r="I104" t="n">
-        <v>0.42</v>
+        <v>0.2466</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.1367</v>
+        <v>-0.1552</v>
       </c>
       <c r="K104" t="n">
-        <v>0.0572</v>
+        <v>0.0401</v>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
@@ -8687,16 +9273,22 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="N104" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="O104" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="P104" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="105">
@@ -8716,28 +9308,28 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E105" t="n">
-        <v>0.065</v>
+        <v>0.0664</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1356</v>
+        <v>0.1384</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0366</v>
+        <v>0.0367</v>
       </c>
       <c r="H105" t="n">
-        <v>1.776</v>
+        <v>1.811</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0774</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.0072</v>
+        <v>-0.006</v>
       </c>
       <c r="K105" t="n">
-        <v>0.1372</v>
+        <v>0.1387</v>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
@@ -8745,16 +9337,22 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="N105" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="O105" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="106">
@@ -8774,28 +9372,28 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5047</v>
+        <v>0.4996</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1293</v>
+        <v>0.1292</v>
       </c>
       <c r="G106" t="n">
-        <v>0.4432</v>
+        <v>0.4397</v>
       </c>
       <c r="H106" t="n">
-        <v>1.139</v>
+        <v>1.136</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2563</v>
+        <v>0.2573</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.3698</v>
+        <v>-0.368</v>
       </c>
       <c r="K106" t="n">
-        <v>1.3792</v>
+        <v>1.3673</v>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
@@ -8803,16 +9401,22 @@
         </is>
       </c>
       <c r="M106" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="N106" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="O106" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="P106" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="107">
@@ -8832,28 +9436,28 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E107" t="n">
-        <v>0.4337</v>
+        <v>0.4248</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0655</v>
+        <v>0.0648</v>
       </c>
       <c r="G107" t="n">
-        <v>0.6187</v>
+        <v>0.6138</v>
       </c>
       <c r="H107" t="n">
-        <v>0.701</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4841</v>
+        <v>0.4897</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.787</v>
+        <v>-0.7864</v>
       </c>
       <c r="K107" t="n">
-        <v>1.6544</v>
+        <v>1.636</v>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
@@ -8861,16 +9465,22 @@
         </is>
       </c>
       <c r="M107" t="n">
-        <v>0.0926</v>
+        <v>0.1026</v>
       </c>
       <c r="N107" t="n">
-        <v>0.0065</v>
+        <v>0.0177</v>
       </c>
       <c r="O107" t="n">
-        <v>2.309</v>
+        <v>1.758</v>
       </c>
       <c r="P107" t="n">
-        <v>0.0222</v>
+        <v>0.1754</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="108">
@@ -8922,12 +9532,18 @@
         <v>0.1027</v>
       </c>
       <c r="N108" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O108" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q108" t="n">
         <v>2.252</v>
       </c>
-      <c r="P108" t="n">
+      <c r="R108" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -8980,12 +9596,18 @@
         <v>0.1027</v>
       </c>
       <c r="N109" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O109" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q109" t="n">
         <v>2.252</v>
       </c>
-      <c r="P109" t="n">
+      <c r="R109" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -9038,12 +9660,18 @@
         <v>0.1027</v>
       </c>
       <c r="N110" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O110" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q110" t="n">
         <v>2.252</v>
       </c>
-      <c r="P110" t="n">
+      <c r="R110" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -9096,12 +9724,18 @@
         <v>0.1027</v>
       </c>
       <c r="N111" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O111" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q111" t="n">
         <v>2.252</v>
       </c>
-      <c r="P111" t="n">
+      <c r="R111" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -9154,12 +9788,18 @@
         <v>0.1027</v>
       </c>
       <c r="N112" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O112" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q112" t="n">
         <v>2.252</v>
       </c>
-      <c r="P112" t="n">
+      <c r="R112" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -9212,12 +9852,18 @@
         <v>0.1027</v>
       </c>
       <c r="N113" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O113" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q113" t="n">
         <v>2.252</v>
       </c>
-      <c r="P113" t="n">
+      <c r="R113" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -9270,12 +9916,18 @@
         <v>0.1027</v>
       </c>
       <c r="N114" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O114" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q114" t="n">
         <v>2.252</v>
       </c>
-      <c r="P114" t="n">
+      <c r="R114" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -9328,12 +9980,18 @@
         <v>0.1027</v>
       </c>
       <c r="N115" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O115" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q115" t="n">
         <v>2.252</v>
       </c>
-      <c r="P115" t="n">
+      <c r="R115" t="n">
         <v>0.0208</v>
       </c>
     </row>
@@ -9386,12 +10044,18 @@
         <v>0.1027</v>
       </c>
       <c r="N116" t="n">
-        <v>0.0101</v>
+        <v>0.0001</v>
       </c>
       <c r="O116" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="Q116" t="n">
         <v>2.252</v>
       </c>
-      <c r="P116" t="n">
+      <c r="R116" t="n">
         <v>0.0208</v>
       </c>
     </row>
